--- a/sampleprojects/TaxReturn/excel/states/MO.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MO.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $29,200 std ded, 4.95%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 29200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0495</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 29200.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0495</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $21,900 std ded, 4.95%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 21900.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0495</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 21900.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0495</t>
   </si>
   <si>
     <t>Default (Single/MFS): $14,600 std ded, 4.95%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 14600.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0495</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 14600.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0495</t>
   </si>
   <si>
     <t>Policy:</t>
